--- a/artfynd/A 18882-2019 artfynd.xlsx
+++ b/artfynd/A 18882-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18882-2019 artfynd.xlsx
+++ b/artfynd/A 18882-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,6 +1370,643 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104789676</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96498</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brutorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>754092</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7197161</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanna Kühne, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104789707</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96498</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brutorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>754056</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7197193</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johanna Kühne, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104789706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96504</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brutorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>754043</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7197182</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johanna Kühne, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104793729</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96498</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brutorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>754004</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7197229</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johanna Kühne, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104789708</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96498</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brutorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>754059</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7197185</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johanna Kühne, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104789709</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96498</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brutorp, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>754080</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7197162</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johanna Kühne, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
